--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK112"/>
+  <dimension ref="A1:AK105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.5</v>
       </c>
     </row>
     <row r="54">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="61">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="72">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="76">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,27 +10561,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="80">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="83">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="93">
@@ -12367,27 +12367,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,27 +12625,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="96">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="99">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="102">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.77083333334</v>
       </c>
     </row>
     <row r="103">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.83333333334</v>
       </c>
     </row>
     <row r="104">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.85416666666</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,909 +14035,6 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45907.72916666666</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Cavalier</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK106" s="3" t="n">
-        <v>45907.72916666666</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Patronato</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK107" s="3" t="n">
-        <v>45907.75</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK108" s="3" t="n">
-        <v>45907.75</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Operário PR</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK109" s="3" t="n">
-        <v>45907.77083333334</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK110" s="3" t="n">
-        <v>45907.83333333334</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" s="3" t="n">
-        <v>45907.85416666666</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK105"/>
+  <dimension ref="A1:AK106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="71">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="73">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="76">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="77">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="80">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="81">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="84">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="92">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12367,27 +12367,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="94">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="102">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.77083333334</v>
       </c>
     </row>
     <row r="104">
@@ -13786,12 +13786,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45907.85416666666</v>
+        <v>45907.83333333334</v>
       </c>
     </row>
     <row r="105">
@@ -13915,126 +13915,255 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK105" s="3" t="n">
+        <v>45907.85416666666</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="inlineStr">
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" t="n">
-        <v>0</v>
-      </c>
-      <c r="W105" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK105" s="3" t="n">
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK106" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK106"/>
+  <dimension ref="A1:AK113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,27 +12496,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="96">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="100">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="103">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="104">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45907.85416666666</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,126 +14044,1029 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Cobreloa</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK106" s="3" t="n">
+        <v>45907.72916666666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" s="3" t="n">
+        <v>45907.72916666666</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" s="3" t="n">
+        <v>45907.75</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Gotham FC</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="3" t="n">
+        <v>45907.75</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" s="3" t="n">
+        <v>45907.77083333334</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="3" t="n">
+        <v>45907.83333333334</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" s="3" t="n">
+        <v>45907.85416666666</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ106" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK106" s="3" t="n">
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G106" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK113"/>
+  <dimension ref="A1:AK112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.03</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="71">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="73">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="77">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="80">
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="81">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="84">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="89">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="95">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="100">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="108">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.77083333334</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.83333333334</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.85416666666</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,135 +14938,6 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45907.85416666666</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK112"/>
+  <dimension ref="A1:AK109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45907.5</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="54">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,16 +9480,16 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -10303,27 +10303,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="78">
@@ -10432,27 +10432,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,61 +10473,61 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="79">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="80">
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="81">
@@ -10819,27 +10819,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="82">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="83">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -11464,27 +11464,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="87">
@@ -11593,27 +11593,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="88">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="94">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="99">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.77083333334</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.83333333334</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.85416666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>7.52</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14551,394 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45907.77083333334</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L110" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="M110" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N110" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK110" s="3" t="n">
-        <v>45907.83333333334</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Goiás</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" s="3" t="n">
-        <v>45907.85416666666</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>45907</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" s="3" t="n">
-        <v>45907.89583333334</v>
+        <v>45907.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK109"/>
+  <dimension ref="A1:AK112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.5</v>
       </c>
     </row>
     <row r="54">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9013,27 +9013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9262,7 +9262,7 @@
         <v>0</v>
       </c>
       <c r="AK68" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="69">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,16 +9480,16 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="77">
@@ -10303,27 +10303,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="78">
@@ -10432,27 +10432,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,61 +10473,61 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X78" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="80">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="81">
@@ -10819,27 +10819,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="83">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11335,27 +11335,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="86">
@@ -11464,27 +11464,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -11593,27 +11593,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="94">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="99">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13786,27 +13786,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13906,7 +13906,7 @@
         <v>0</v>
       </c>
       <c r="AK104" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="105">
@@ -13915,27 +13915,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14035,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="AK105" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="106">
@@ -14044,27 +14044,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="107">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="108">
@@ -14302,12 +14302,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45907.85416666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="109">
@@ -14431,126 +14431,513 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N109" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="3" t="n">
+        <v>45907.77083333334</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M110" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N110" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" s="3" t="n">
+        <v>45907.83333333334</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N111" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="3" t="n">
+        <v>45907.85416666666</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="inlineStr">
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L109" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M109" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="N109" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK109" s="3" t="n">
+      <c r="L112" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M112" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" s="3" t="n">
         <v>45907.875</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45907.875</v>
+        <v>45907.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45907.39583333334</v>
+        <v>45907.41666666666</v>
       </c>
     </row>
     <row r="32">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45907.41666666666</v>
+        <v>45907.45833333334</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45907.45833333334</v>
+        <v>45907.46875</v>
       </c>
     </row>
     <row r="42">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45907.46875</v>
+        <v>45907.47916666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45907.47916666666</v>
+        <v>45907.48958333334</v>
       </c>
     </row>
     <row r="45">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.55</v>
+        <v>1.8</v>
       </c>
       <c r="M89" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N89" t="n">
-        <v>1.66</v>
+        <v>4.5</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G106" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>3.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.29</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>3.76</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45907.5</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="54">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="61">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="70">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="72">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="75">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="76">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="79">
@@ -10561,27 +10561,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="80">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="83">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N96" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK112"/>
+  <dimension ref="A1:AK113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>2.83</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="M41" t="n">
         <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="72">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="75">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="76">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="79">
@@ -10561,27 +10561,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="80">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
         <v>3.2</v>
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="83">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,27 +11722,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="M99" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="100">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14173,27 +14173,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14293,7 +14293,7 @@
         <v>0</v>
       </c>
       <c r="AK107" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="108">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="110">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="M110" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="N110" t="n">
-        <v>2.7</v>
+        <v>3.53</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.77083333334</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="M111" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="N111" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45907.85416666666</v>
+        <v>45907.83333333334</v>
       </c>
     </row>
     <row r="112">
@@ -14818,126 +14818,255 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N112" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" s="3" t="n">
+        <v>45907.85416666666</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="inlineStr">
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L112" t="n">
+      <c r="L113" t="n">
         <v>1.34</v>
       </c>
-      <c r="M112" t="n">
+      <c r="M113" t="n">
         <v>4.3</v>
       </c>
-      <c r="N112" t="n">
+      <c r="N113" t="n">
         <v>7.2</v>
       </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
         <v>1.76</v>
       </c>
-      <c r="Z112" t="n">
+      <c r="Z113" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" s="3" t="n">
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G109" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="M72" t="n">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N72" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,16 +9738,16 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.17</v>
+        <v>1.84</v>
       </c>
       <c r="M74" t="n">
-        <v>3.37</v>
+        <v>3.76</v>
       </c>
       <c r="N74" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z74" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z74" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,10 +12054,10 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="N92" t="n">
-        <v>1.66</v>
+        <v>4.1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.83</v>
+        <v>3.55</v>
       </c>
       <c r="M93" t="n">
-        <v>3.07</v>
+        <v>4.2</v>
       </c>
       <c r="N93" t="n">
-        <v>4.1</v>
+        <v>1.66</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N96" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45907.41666666666</v>
+        <v>45907.39583333334</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45907.45833333334</v>
+        <v>45907.41666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45907.46875</v>
+        <v>45907.45833333334</v>
       </c>
     </row>
     <row r="42">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45907.47916666666</v>
+        <v>45907.46875</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45907.48958333334</v>
+        <v>45907.47916666666</v>
       </c>
     </row>
     <row r="45">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9271,27 +9271,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="73">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.17</v>
+        <v>1.84</v>
       </c>
       <c r="M73" t="n">
-        <v>3.37</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>2.19</v>
+        <v>3.84</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z73" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z73" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="M74" t="n">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N74" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,16 +9996,16 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="77">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="AK79" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="80">
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="81">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11077,27 +11077,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
         <v>0</v>
       </c>
       <c r="AK83" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="84">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.25</v>
+        <v>3.55</v>
       </c>
       <c r="M89" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="N89" t="n">
-        <v>3.54</v>
+        <v>1.66</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="M90" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="N90" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.83</v>
+        <v>1.49</v>
       </c>
       <c r="M92" t="n">
-        <v>3.07</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="N94" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="X94" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N95" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M96" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N96" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,10 +12828,10 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.05</v>
+        <v>2.15</v>
       </c>
       <c r="M97" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="N97" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,16 +12957,16 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="M98" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,16 +13086,16 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M99" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14376,10 +14376,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>3.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>2.83</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>2.06</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="M11" t="n">
-        <v>2.83</v>
+        <v>3.41</v>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="M89" t="n">
-        <v>4.2</v>
+        <v>3.07</v>
       </c>
       <c r="N89" t="n">
-        <v>1.66</v>
+        <v>4.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="M90" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="N90" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,16 +12054,16 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.49</v>
+        <v>3.55</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>7.2</v>
+        <v>1.66</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="M94" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="X94" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,49 +12795,49 @@
         </is>
       </c>
       <c r="L96" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N96" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
         <v>2.4</v>
       </c>
-      <c r="M96" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N96" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X96" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M97" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="N97" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,10 +12957,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X97" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.05</v>
+        <v>1.7</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="N99" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.55</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="N7" t="n">
-        <v>2.06</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="M89" t="n">
-        <v>3.07</v>
+        <v>2.65</v>
       </c>
       <c r="N89" t="n">
         <v>4.1</v>
@@ -11925,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="M90" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,10 +12054,10 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="X90" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="N94" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,16 +12570,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="M95" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="N95" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="M97" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,16 +12957,16 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N98" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M99" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="N99" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X99" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.56</v>
+        <v>2.14</v>
       </c>
       <c r="M109" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="M89" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="N89" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12054,10 +12054,10 @@
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12153,10 +12153,10 @@
         <v>2.1</v>
       </c>
       <c r="M91" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="N91" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X91" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>1.66</v>
+        <v>7.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="M94" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="N94" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,16 +12570,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M95" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="N95" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="X95" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="M96" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N96" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,16 +12828,16 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>4.1</v>
+        <v>2.17</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13056,10 +13056,10 @@
         <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N98" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="M99" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>4.9</v>
+        <v>4.15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M113" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N113" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,7 +15027,7 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Z113" t="n">
         <v>1.9</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M91" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N91" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X91" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M92" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="N92" t="n">
-        <v>7.7</v>
+        <v>4.15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="X92" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.83</v>
+        <v>3.8</v>
       </c>
       <c r="M93" t="n">
-        <v>3.07</v>
+        <v>4.5</v>
       </c>
       <c r="N93" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="M94" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>4.8</v>
+        <v>7.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="X94" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="M96" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>4.5</v>
+        <v>2.17</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,16 +12828,16 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="M98" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N98" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="X98" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="N99" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N108" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>3.76</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="M91" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="N91" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,16 +12183,16 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M92" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N92" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X92" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="M93" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,16 +12441,16 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="N94" t="n">
-        <v>7.7</v>
+        <v>4.15</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="X94" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="M95" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N95" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="X95" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="M96" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,14 +13182,14 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="M99" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N99" t="n">
         <v>2.95</v>
       </c>
-      <c r="N99" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
@@ -13215,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="X99" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N42" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="M89" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="N89" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="M92" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M94" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N94" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,10 +12570,10 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X94" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Y94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="M95" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N95" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="X95" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="N97" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,16 +12957,16 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N98" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X98" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="M99" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>2.17</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.42</v>
+        <v>3.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.08</v>
+        <v>2.19</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N43" t="n">
-        <v>2.19</v>
+        <v>3.08</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M89" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N89" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X89" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.8</v>
+        <v>1.83</v>
       </c>
       <c r="M90" t="n">
-        <v>4.5</v>
+        <v>3.07</v>
       </c>
       <c r="N90" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="M92" t="n">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="N92" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="M94" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="N94" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,16 +12570,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M95" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N95" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,10 +12699,10 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X95" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Y95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M97" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N97" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,10 +12957,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X97" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,14 +13053,14 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="M98" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N98" t="n">
         <v>2.95</v>
       </c>
-      <c r="N98" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
@@ -13086,10 +13086,10 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="X98" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Y98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>2.17</v>
+        <v>4.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="M108" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N108" t="n">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK113"/>
+  <dimension ref="A1:AK116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45907.48958333334</v>
+        <v>45907.47916666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45907.5</v>
+        <v>45907.47916666666</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45907.5</v>
+        <v>45907.48958333334</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.5</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45907.52083333334</v>
+        <v>45907.5</v>
       </c>
     </row>
     <row r="55">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45907.54166666666</v>
+        <v>45907.52083333334</v>
       </c>
     </row>
     <row r="62">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45907.55208333334</v>
+        <v>45907.54166666666</v>
       </c>
     </row>
     <row r="72">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45907.5625</v>
+        <v>45907.55208333334</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45907.57291666666</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="77">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10423,7 +10423,7 @@
         <v>0</v>
       </c>
       <c r="AK77" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.5625</v>
       </c>
     </row>
     <row r="78">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10552,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="AK78" s="3" t="n">
-        <v>45907.58333333334</v>
+        <v>45907.57291666666</v>
       </c>
     </row>
     <row r="79">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10810,7 +10810,7 @@
         <v>0</v>
       </c>
       <c r="AK80" s="3" t="n">
-        <v>45907.60416666666</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="81">
@@ -10819,27 +10819,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.58333333334</v>
       </c>
     </row>
     <row r="82">
@@ -10948,27 +10948,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11068,7 +11068,7 @@
         <v>0</v>
       </c>
       <c r="AK82" s="3" t="n">
-        <v>45907.625</v>
+        <v>45907.60416666666</v>
       </c>
     </row>
     <row r="83">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11206,12 +11206,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="85">
@@ -11335,12 +11335,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11455,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AK85" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="86">
@@ -11464,27 +11464,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45907.64583333334</v>
+        <v>45907.625</v>
       </c>
     </row>
     <row r="87">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11851,27 +11851,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11925,10 +11925,10 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,27 +11980,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,27 +12109,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12183,10 +12183,10 @@
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45907.66666666666</v>
+        <v>45907.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M92" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="N92" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X92" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="M94" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N94" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,16 +12570,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="M95" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="N95" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,16 +12699,16 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="96">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="M96" t="n">
-        <v>3.25</v>
+        <v>3.07</v>
       </c>
       <c r="N96" t="n">
-        <v>2.17</v>
+        <v>4.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="97">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,10 +12957,10 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X97" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45907.70833333334</v>
+        <v>45907.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="M98" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,16 +13086,16 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,10 +13344,10 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y100" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="102">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,10 +13602,10 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45907.72916666666</v>
+        <v>45907.70833333334</v>
       </c>
     </row>
     <row r="103">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14302,27 +14302,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,10 +14376,10 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
         <v>0</v>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="AK108" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="109">
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45907.75</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45907.77083333334</v>
+        <v>45907.72916666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="M111" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45907.83333333334</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="M112" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="N112" t="n">
-        <v>2.66</v>
+        <v>5.3</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45907.85416666666</v>
+        <v>45907.75</v>
       </c>
     </row>
     <row r="113">
@@ -14947,126 +14947,513 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N113" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" s="3" t="n">
+        <v>45907.77083333334</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M114" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N114" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK114" s="3" t="n">
+        <v>45907.83333333334</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N115" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" s="3" t="n">
+        <v>45907.85416666666</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45907</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="inlineStr">
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L113" t="n">
+      <c r="L116" t="n">
         <v>1.38</v>
       </c>
-      <c r="M113" t="n">
+      <c r="M116" t="n">
         <v>4.4</v>
       </c>
-      <c r="N113" t="n">
+      <c r="N116" t="n">
         <v>7.5</v>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y113" t="n">
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z113" t="n">
+      <c r="Z116" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK113" s="3" t="n">
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="3" t="n">
         <v>45907.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="M92" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12312,16 +12312,16 @@
         <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M95" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="N95" t="n">
-        <v>1.7</v>
+        <v>4.15</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,16 +12699,16 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="M96" t="n">
-        <v>3.07</v>
+        <v>2.6</v>
       </c>
       <c r="N96" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,16 +12828,16 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N98" t="n">
-        <v>4.4</v>
+        <v>2.17</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N99" t="n">
-        <v>2.17</v>
+        <v>3.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M100" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="M76" t="n">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N76" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11314,10 +11314,10 @@
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.83</v>
+        <v>3.8</v>
       </c>
       <c r="M92" t="n">
-        <v>3.07</v>
+        <v>4.5</v>
       </c>
       <c r="N92" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,10 +12441,10 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y93" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="M95" t="n">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="N95" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12699,16 +12699,16 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="N96" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12828,10 +12828,10 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X96" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Y96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,14 +13182,14 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="M99" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N99" t="n">
         <v>2.95</v>
       </c>
-      <c r="N99" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
@@ -13215,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="X99" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="N100" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M101" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N101" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13473,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="X101" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="Y101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="M102" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>2.95</v>
+        <v>4.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="M111" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="N111" t="n">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="M112" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N112" t="n">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.41</v>
+        <v>2.83</v>
       </c>
       <c r="N18" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Telstar W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Telstar W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,61 +9570,61 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,16 +10125,16 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="M77" t="n">
-        <v>3.76</v>
+        <v>3.37</v>
       </c>
       <c r="N77" t="n">
-        <v>3.84</v>
+        <v>2.19</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,49 +12279,49 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.8</v>
+        <v>2.07</v>
       </c>
       <c r="M92" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="N92" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
         <v>1.7</v>
       </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="M93" t="n">
-        <v>2.6</v>
+        <v>3.07</v>
       </c>
       <c r="N93" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12441,16 +12441,16 @@
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="M94" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N94" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12570,16 +12570,16 @@
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="M96" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="N96" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>2.05</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12957,16 +12957,16 @@
         <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="M98" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N98" t="n">
-        <v>2.17</v>
+        <v>4.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13086,16 +13086,16 @@
         <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="M99" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N99" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="X99" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.98</v>
+        <v>3.2</v>
       </c>
       <c r="M100" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N100" t="n">
-        <v>4.5</v>
+        <v>2.17</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="M101" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13473,16 +13473,16 @@
         <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="M102" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="N102" t="n">
-        <v>4.4</v>
+        <v>2.95</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>2.3</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="M114" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>

--- a/jogos_2025-09-07.xlsx
+++ b/jogos_2025-09-07.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="M16" t="n">
-        <v>3.41</v>
+        <v>3.29</v>
       </c>
       <c r="N16" t="n">
-        <v>1.97</v>
+        <v>3.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
         <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
         <v>1.28</v>
@@ -2514,38 +2514,38 @@
         <v>3.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,37 +2604,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.82</v>
+        <v>3.12</v>
       </c>
       <c r="M17" t="n">
-        <v>3.29</v>
+  